--- a/AAII_Financials/Quarterly/HNNMY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/HNNMY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="443" uniqueCount="92">
   <si>
     <t>HNNMY</t>
   </si>
@@ -656,84 +656,92 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46265</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46173</v>
+      </c>
+      <c r="F7" s="2">
         <v>46081</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45991</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45900</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45808</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45716</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45626</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45535</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45443</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45351</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45260</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>45169</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>45077</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44985</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44895</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -779,8 +787,14 @@
       <c r="Q8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -826,8 +840,14 @@
       <c r="Q9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -873,8 +893,14 @@
       <c r="Q10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -892,8 +918,10 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -939,8 +967,14 @@
       <c r="Q12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -986,8 +1020,14 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+      <c r="S13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1033,8 +1073,14 @@
       <c r="Q14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1080,8 +1126,14 @@
       <c r="Q15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1096,8 +1148,10 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1143,8 +1197,14 @@
       <c r="Q17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1190,8 +1250,14 @@
       <c r="Q18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1209,8 +1275,10 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1256,8 +1324,14 @@
       <c r="Q20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1303,8 +1377,14 @@
       <c r="Q21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1350,8 +1430,14 @@
       <c r="Q22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1397,8 +1483,14 @@
       <c r="Q23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1444,8 +1536,14 @@
       <c r="Q24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1491,8 +1589,14 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+      <c r="S25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1538,8 +1642,14 @@
       <c r="Q26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1585,8 +1695,14 @@
       <c r="Q27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1632,8 +1748,14 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+      <c r="S28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1679,8 +1801,14 @@
       <c r="Q29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1726,8 +1854,14 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+      <c r="S30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1773,8 +1907,14 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+      <c r="S31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1820,8 +1960,14 @@
       <c r="Q32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1867,8 +2013,14 @@
       <c r="Q33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1914,8 +2066,14 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+      <c r="S34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1961,60 +2119,72 @@
       <c r="Q35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46265</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46173</v>
+      </c>
+      <c r="F38" s="2">
         <v>46081</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45991</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45900</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45808</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45716</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45626</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45535</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45443</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45351</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45260</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>45169</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>45077</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44985</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44895</v>
       </c>
     </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2032,8 +2202,10 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2051,55 +2223,63 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2766900</v>
+      </c>
+      <c r="E41" s="3">
+        <v>2027900</v>
+      </c>
+      <c r="F41" s="3">
         <v>2076300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>2212800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>2149100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>1695600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>1544800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>1588200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>2309500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>2301600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>2008500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>2528000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>2282100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>1849900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>2042400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>2043500</v>
       </c>
     </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2145,337 +2325,385 @@
       <c r="Q42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R42" s="3">
+        <v>0</v>
+      </c>
+      <c r="S42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1660800</v>
+      </c>
+      <c r="E43" s="3">
+        <v>1680600</v>
+      </c>
+      <c r="F43" s="3">
         <v>1534300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>1307500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>1667900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>1651900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>1428900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>1180800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>1522200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>1475600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>1498400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>1068000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>1548700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>1558300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>1413000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>955200</v>
       </c>
     </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>4108100</v>
+      </c>
+      <c r="E44" s="3">
+        <v>3789900</v>
+      </c>
+      <c r="F44" s="3">
         <v>3835800</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>3749400</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>4003900</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>4047200</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>3821400</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>3695600</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>4067500</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>3656500</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>3629800</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>3577500</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>3688300</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>3559000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>3937000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>4000500</v>
       </c>
     </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>66300</v>
+      </c>
+      <c r="E45" s="3">
+        <v>34600</v>
+      </c>
+      <c r="F45" s="3">
         <v>79600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>53200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>60200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>160300</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>93400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>112100</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>73400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>49500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>85100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>104300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>101000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>112500</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>57900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>64100</v>
       </c>
     </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>8602100</v>
+      </c>
+      <c r="E46" s="3">
+        <v>7533000</v>
+      </c>
+      <c r="F46" s="3">
         <v>7526000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>7672400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>7881000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>7554900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>6888500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>6936100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>7972600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>7483200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>7221700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>7711700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>7620100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>7079700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>7450400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>7486400</v>
       </c>
     </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>159500</v>
+      </c>
+      <c r="E47" s="3">
+        <v>175200</v>
+      </c>
+      <c r="F47" s="3">
         <v>173500</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>216400</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>259300</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>267600</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>272300</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>301200</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>288500</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>275100</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>257100</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>246300</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>248400</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>231400</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>271600</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>297200</v>
       </c>
     </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>8773200</v>
+      </c>
+      <c r="E48" s="3">
+        <v>8851800</v>
+      </c>
+      <c r="F48" s="3">
         <v>9053500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>8734900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>8560500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>8263800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>8065300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>7897200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>7788100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>7771300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>7731300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>7808200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>7637300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>7690700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>7777000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>7788800</v>
       </c>
     </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>738900</v>
+      </c>
+      <c r="E49" s="3">
+        <v>800600</v>
+      </c>
+      <c r="F49" s="3">
         <v>844800</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>169500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>839900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>864300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>792400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>149800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>878500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>862900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>882400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>168400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>928900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>960800</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>1012100</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>21200</v>
       </c>
     </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2521,8 +2749,14 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+      <c r="S50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2568,55 +2802,67 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+      <c r="S51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>625600</v>
+      </c>
+      <c r="E52" s="3">
+        <v>631600</v>
+      </c>
+      <c r="F52" s="3">
         <v>589500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>82000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>597100</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>596400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>565100</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>78700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>674800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>670200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>668900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>115300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>704900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>712700</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>705800</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>88400</v>
       </c>
     </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2662,55 +2908,67 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+      <c r="S53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>18899300</v>
+      </c>
+      <c r="E54" s="3">
+        <v>17992000</v>
+      </c>
+      <c r="F54" s="3">
         <v>18187300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>18020600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>18137800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>17547000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>16583600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>16506300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>17602500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>17062600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>16761500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>17359300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>17139500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>16675300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>17216800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>17138100</v>
       </c>
     </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2728,8 +2986,10 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2747,290 +3007,328 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E57" s="3">
+      <c r="E57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G57" s="3">
         <v>2204100</v>
       </c>
-      <c r="F57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G57" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H57" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I57" s="3">
+      <c r="I57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K57" s="3">
         <v>2236400</v>
       </c>
-      <c r="J57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K57" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L57" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M57" s="3">
+      <c r="M57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O57" s="3">
         <v>2013600</v>
       </c>
-      <c r="N57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O57" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P57" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="Q57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S57" s="3">
         <v>1985400</v>
       </c>
     </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1325700</v>
+      </c>
+      <c r="E58" s="3">
+        <v>1329000</v>
+      </c>
+      <c r="F58" s="3">
         <v>1563900</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>1514900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>1247500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>1802600</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>1214500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>1142700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>1165500</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>1365800</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>1223600</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>1451500</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>1442100</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>1520100</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>1240700</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>1290700</v>
       </c>
     </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>6270900</v>
+      </c>
+      <c r="E59" s="3">
+        <v>5728900</v>
+      </c>
+      <c r="F59" s="3">
         <v>4803800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>946000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>6281000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>5781500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>4797700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>879800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>5993700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>5534500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>4779700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>862800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>5590200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>5236800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>4977000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>798800</v>
       </c>
     </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>7596600</v>
+      </c>
+      <c r="E60" s="3">
+        <v>7057900</v>
+      </c>
+      <c r="F60" s="3">
         <v>6367700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>6519700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>7528400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>7584100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>6012200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>6104700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>7159200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>6900400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>6003300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>6504900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>7032400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>6756900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>6217600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>6433100</v>
       </c>
     </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>6960000</v>
+      </c>
+      <c r="E61" s="3">
+        <v>6999900</v>
+      </c>
+      <c r="F61" s="3">
         <v>6949700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>6692200</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>6221800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>5838000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>6011200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>5905700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>5977800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>5968100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>5970100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>6015200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>5366700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>5432800</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>5651500</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>5547200</v>
       </c>
     </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>177100</v>
+      </c>
+      <c r="E62" s="3">
+        <v>212400</v>
+      </c>
+      <c r="F62" s="3">
         <v>230000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>15700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>196200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>267400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>218900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>14800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>184100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>229300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>238600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>13100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>323900</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>332100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>347400</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>40000</v>
       </c>
     </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3076,8 +3374,14 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+      <c r="S63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3123,8 +3427,14 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+      <c r="S64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3170,55 +3480,67 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+      <c r="S65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>14769900</v>
+      </c>
+      <c r="E66" s="3">
+        <v>14312600</v>
+      </c>
+      <c r="F66" s="3">
         <v>13595900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>13475400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>13998900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>13739300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>12285800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>12273700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>13389400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>13147200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>12258100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>12809600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>12764000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>12556800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>12249500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>12359800</v>
       </c>
     </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3236,8 +3558,10 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3283,8 +3607,14 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+      <c r="S68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3330,8 +3660,14 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+      <c r="S69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3377,8 +3713,14 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3424,55 +3766,67 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+      <c r="S71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E72" s="3">
+      <c r="E72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G72" s="3">
         <v>4171600</v>
       </c>
-      <c r="F72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H72" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I72" s="3">
+      <c r="I72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K72" s="3">
         <v>3617000</v>
       </c>
-      <c r="J72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L72" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M72" s="3">
+      <c r="M72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O72" s="3">
         <v>3928700</v>
       </c>
-      <c r="N72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P72" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="Q72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S72" s="3">
         <v>4207500</v>
       </c>
     </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3518,8 +3872,14 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+      <c r="S73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3565,8 +3925,14 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+      <c r="S74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3612,55 +3978,67 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+      <c r="S75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>4122100</v>
+      </c>
+      <c r="E76" s="3">
+        <v>3681400</v>
+      </c>
+      <c r="F76" s="3">
         <v>4590800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>4542500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>4133200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>3807800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>4292400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>4226300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>4207000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>3909100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>4494400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>4541900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>4367100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>4108600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>4958900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>4778300</v>
       </c>
     </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3706,60 +4084,72 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+      <c r="S77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46265</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46173</v>
+      </c>
+      <c r="F80" s="2">
         <v>46081</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45991</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45900</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45808</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45716</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45626</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45535</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45443</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45351</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45260</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>45169</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>45077</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44985</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44895</v>
       </c>
     </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -3805,8 +4195,14 @@
       <c r="Q81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3824,55 +4220,63 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>537300</v>
+      </c>
+      <c r="E83" s="3">
+        <v>526400</v>
+      </c>
+      <c r="F83" s="3">
         <v>507800</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>290000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>523700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>515300</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>521200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>326800</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>527600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>502600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>519200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>240600</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>582000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>533000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>571200</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="S83" s="3">
         <v>437700</v>
       </c>
     </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3918,8 +4322,14 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+      <c r="S84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3965,8 +4375,14 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+      <c r="S85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4012,8 +4428,14 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+      <c r="S86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4059,8 +4481,14 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+      <c r="S87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4106,55 +4534,67 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+      <c r="S88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1243000</v>
+      </c>
+      <c r="E89" s="3">
+        <v>1148700</v>
+      </c>
+      <c r="F89" s="3">
         <v>446100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>889600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>1053800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>889200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>391500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>638800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>800600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>1196100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>382700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>881700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>1120200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>687800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>478300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>614200</v>
       </c>
     </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4172,55 +4612,63 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-170300</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-166200</v>
+      </c>
+      <c r="F91" s="3">
         <v>-190600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-316700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-253800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-226500</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-155700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-367400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-250700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-207100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-124800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-305200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-195900</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-131000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-117700</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-182500</v>
       </c>
     </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4266,8 +4714,14 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+      <c r="S92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4313,55 +4767,67 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+      <c r="S93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-179600</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-184400</v>
+      </c>
+      <c r="F94" s="3">
         <v>-236000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-342200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-290400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-268700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-191300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-366500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-324900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-245200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-159700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-360400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-216900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-168800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-157600</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-237800</v>
       </c>
     </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4379,55 +4845,63 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3" t="s">
-        <v>4</v>
+      <c r="D96" s="3">
+        <v>0</v>
       </c>
       <c r="E96" s="3">
+        <v>615200</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G96" s="3">
         <v>576900</v>
       </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
+        <v>0</v>
+      </c>
+      <c r="I96" s="3">
         <v>568800</v>
       </c>
-      <c r="H96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K96" s="3">
         <v>478200</v>
       </c>
-      <c r="J96" s="3">
-        <v>0</v>
-      </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
+        <v>0</v>
+      </c>
+      <c r="M96" s="3">
         <v>497000</v>
       </c>
-      <c r="L96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O96" s="3">
         <v>505600</v>
       </c>
-      <c r="N96" s="3">
-        <v>0</v>
-      </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="3">
         <v>485900</v>
       </c>
-      <c r="P96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S96" s="3">
         <v>499700</v>
       </c>
     </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4473,8 +4947,14 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+      <c r="S97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4520,8 +5000,14 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+      <c r="S98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4567,145 +5053,169 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+      <c r="S99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-286900</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-973800</v>
+      </c>
+      <c r="F100" s="3">
         <v>-425200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-519300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-327500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-581100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-253900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-871900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-503800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-645700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-744100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-345800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-421900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-667900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-297900</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>-906800</v>
       </c>
     </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="E101" s="3">
+        <v>-72400</v>
+      </c>
+      <c r="F101" s="3">
         <v>-17200</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>17200</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>-25200</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>19800</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>-16700</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>-38900</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>-42500</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>46000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>-62800</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>-19400</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>147300</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>15700</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>21800</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="S101" s="3">
         <v>91300</v>
       </c>
     </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>815200</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="F102" s="3">
         <v>-241100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>57700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>432800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-32900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-71000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-582300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-53400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>325000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-537900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>136700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>438900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-102800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-40000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>-549800</v>
       </c>
     </row>
